--- a/jpg-ocr-stat/evaluation/group_03/stat_oracle.xlsx
+++ b/jpg-ocr-stat/evaluation/group_03/stat_oracle.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="results" sheetId="1" r:id="Rf8e4d85c71244a54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="results" sheetId="1" r:id="Recccd540259d4e83"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -469,7 +469,7 @@
         <x:v>2018-03-26</x:v>
       </x:c>
       <x:c r="C19" s="2" t="str">
-        <x:v>60.60</x:v>
+        <x:v>33.00</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="20" customHeight="1">

--- a/jpg-ocr-stat/evaluation/group_03/stat_oracle.xlsx
+++ b/jpg-ocr-stat/evaluation/group_03/stat_oracle.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="results" sheetId="1" r:id="Recccd540259d4e83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="results" sheetId="1" r:id="Rf0ff73e2567e41d6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -276,222 +276,222 @@
     </x:row>
     <x:row r="2" ht="20" customHeight="1">
       <x:c r="A2" s="2" t="str">
-        <x:v>X51005447840.png</x:v>
+        <x:v>receipt_0001.png</x:v>
       </x:c>
       <x:c r="B2" s="2" t="str">
-        <x:v>2018-03-14</x:v>
+        <x:v>2018-03-15</x:v>
       </x:c>
       <x:c r="C2" s="2" t="str">
-        <x:v>8.20</x:v>
+        <x:v>8.00</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="20" customHeight="1">
       <x:c r="A3" s="2" t="str">
-        <x:v>X51005447850.png</x:v>
+        <x:v>receipt_0015.png</x:v>
       </x:c>
       <x:c r="B3" s="2" t="str">
-        <x:v>2018-03-04</x:v>
+        <x:v>2018-03-01</x:v>
       </x:c>
       <x:c r="C3" s="2" t="str">
-        <x:v>3.20</x:v>
+        <x:v>49.40</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="20" customHeight="1">
       <x:c r="A4" s="2" t="str">
-        <x:v>X51005447861.png</x:v>
+        <x:v>receipt_0029.png</x:v>
       </x:c>
       <x:c r="B4" s="2" t="str">
-        <x:v>2018-03-01</x:v>
+        <x:v>2018-01-03</x:v>
       </x:c>
       <x:c r="C4" s="2" t="str">
-        <x:v>49.40</x:v>
+        <x:v>94.87</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="20" customHeight="1">
       <x:c r="A5" s="2" t="str">
-        <x:v>X51005568884.png</x:v>
+        <x:v>receipt_0043.png</x:v>
       </x:c>
       <x:c r="B5" s="2" t="str">
-        <x:v>2017-11-24</x:v>
+        <x:v>2018-03-22</x:v>
       </x:c>
       <x:c r="C5" s="2" t="str">
-        <x:v>3.90</x:v>
+        <x:v>101.75</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="20" customHeight="1">
       <x:c r="A6" s="2" t="str">
-        <x:v>X51005568887.png</x:v>
+        <x:v>receipt_0044.png</x:v>
       </x:c>
       <x:c r="B6" s="2" t="str">
-        <x:v>2017-04-26</x:v>
+        <x:v>2018-05-04</x:v>
       </x:c>
       <x:c r="C6" s="2" t="str">
-        <x:v>7.20</x:v>
+        <x:v>19.00</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="20" customHeight="1">
       <x:c r="A7" s="2" t="str">
-        <x:v>X51005568894.png</x:v>
+        <x:v>receipt_0087.png</x:v>
       </x:c>
       <x:c r="B7" s="2" t="str">
-        <x:v>2017-01-17</x:v>
+        <x:v>2017-12-04</x:v>
       </x:c>
       <x:c r="C7" s="2" t="str">
-        <x:v>46.65</x:v>
+        <x:v>42.40</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="20" customHeight="1">
       <x:c r="A8" s="2" t="str">
-        <x:v>X51005675099.png</x:v>
+        <x:v>receipt_0100.png</x:v>
       </x:c>
       <x:c r="B8" s="2" t="str">
-        <x:v>2018-01-20</x:v>
+        <x:v>2018-01-02</x:v>
       </x:c>
       <x:c r="C8" s="2" t="str">
-        <x:v>132.50</x:v>
+        <x:v>13.25</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="20" customHeight="1">
       <x:c r="A9" s="2" t="str">
-        <x:v>X51005676534.png</x:v>
+        <x:v>receipt_0109.png</x:v>
       </x:c>
       <x:c r="B9" s="2" t="str">
-        <x:v>2018-01-03</x:v>
+        <x:v>2017-06-03</x:v>
       </x:c>
       <x:c r="C9" s="2" t="str">
-        <x:v>72.08</x:v>
+        <x:v>18.00</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="20" customHeight="1">
       <x:c r="A10" s="2" t="str">
-        <x:v>X51005676539.png</x:v>
+        <x:v>receipt_0111.png</x:v>
       </x:c>
       <x:c r="B10" s="2" t="str">
-        <x:v>2018-01-10</x:v>
+        <x:v>2017-09-27</x:v>
       </x:c>
       <x:c r="C10" s="2" t="str">
-        <x:v>23.32</x:v>
+        <x:v>248.05</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="20" customHeight="1">
       <x:c r="A11" s="2" t="str">
-        <x:v>X51005676543.png</x:v>
+        <x:v>receipt_0119.png</x:v>
       </x:c>
       <x:c r="B11" s="2" t="str">
-        <x:v>2018-01-02</x:v>
+        <x:v>2018-02-02</x:v>
       </x:c>
       <x:c r="C11" s="2" t="str">
-        <x:v>13.25</x:v>
+        <x:v>374.20</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="20" customHeight="1">
       <x:c r="A12" s="2" t="str">
-        <x:v>X51005677328.png</x:v>
+        <x:v>receipt_0120.png</x:v>
       </x:c>
       <x:c r="B12" s="2" t="str">
-        <x:v>2018-02-12</x:v>
+        <x:v>2018-01-17</x:v>
       </x:c>
       <x:c r="C12" s="2" t="str">
-        <x:v>5.30</x:v>
+        <x:v>29.00</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="20" customHeight="1">
       <x:c r="A13" s="2" t="str">
-        <x:v>X51005705722.png</x:v>
+        <x:v>receipt_0131.png</x:v>
       </x:c>
       <x:c r="B13" s="2" t="str">
-        <x:v>2017-09-27</x:v>
+        <x:v>2018-04-14</x:v>
       </x:c>
       <x:c r="C13" s="2" t="str">
-        <x:v>248.05</x:v>
+        <x:v>156.00</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="20" customHeight="1">
       <x:c r="A14" s="2" t="str">
-        <x:v>X51005705759.png</x:v>
+        <x:v>receipt_0150.png</x:v>
       </x:c>
       <x:c r="B14" s="2" t="str">
-        <x:v>2017-08-01</x:v>
+        <x:v>2017-05-05</x:v>
       </x:c>
       <x:c r="C14" s="2" t="str">
-        <x:v>109.90</x:v>
+        <x:v>42.35</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="20" customHeight="1">
       <x:c r="A15" s="2" t="str">
-        <x:v>X51005711401.png</x:v>
+        <x:v>receipt_0158.png</x:v>
       </x:c>
       <x:c r="B15" s="2" t="str">
-        <x:v>2018-03-19</x:v>
+        <x:v>2018-01-23</x:v>
       </x:c>
       <x:c r="C15" s="2" t="str">
-        <x:v>6.00</x:v>
+        <x:v>18.00</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="20" customHeight="1">
       <x:c r="A16" s="2" t="str">
-        <x:v>X51005711452.png</x:v>
+        <x:v>receipt_0161.png</x:v>
       </x:c>
       <x:c r="B16" s="2" t="str">
-        <x:v>2018-03-21</x:v>
+        <x:v>2018-03-30</x:v>
       </x:c>
       <x:c r="C16" s="2" t="str">
-        <x:v>25.40</x:v>
+        <x:v>159.00</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="20" customHeight="1">
       <x:c r="A17" s="2" t="str">
-        <x:v>X51005719888.png</x:v>
+        <x:v>receipt_0180.png</x:v>
       </x:c>
       <x:c r="B17" s="2" t="str">
-        <x:v>2018-01-04</x:v>
+        <x:v>2018-03-28</x:v>
       </x:c>
       <x:c r="C17" s="2" t="str">
-        <x:v>39.80</x:v>
+        <x:v>129.30</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="20" customHeight="1">
       <x:c r="A18" s="2" t="str">
-        <x:v>X51005719905.png</x:v>
+        <x:v>receipt_0186.png</x:v>
       </x:c>
       <x:c r="B18" s="2" t="str">
-        <x:v>2018-03-25</x:v>
+        <x:v>2018-03-29</x:v>
       </x:c>
       <x:c r="C18" s="2" t="str">
-        <x:v>8.20</x:v>
+        <x:v>39.90</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="20" customHeight="1">
       <x:c r="A19" s="2" t="str">
-        <x:v>X51005719917.png</x:v>
+        <x:v>receipt_0187.png</x:v>
       </x:c>
       <x:c r="B19" s="2" t="str">
-        <x:v>2018-03-26</x:v>
+        <x:v>2018-03-29</x:v>
       </x:c>
       <x:c r="C19" s="2" t="str">
-        <x:v>33.00</x:v>
+        <x:v>48.95</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="20" customHeight="1">
       <x:c r="A20" s="2" t="str">
-        <x:v>X51005749905.png</x:v>
+        <x:v>receipt_0188.png</x:v>
       </x:c>
       <x:c r="B20" s="2" t="str">
-        <x:v>2018-03-10</x:v>
+        <x:v>2018-03-27</x:v>
       </x:c>
       <x:c r="C20" s="2" t="str">
-        <x:v>34.00</x:v>
+        <x:v>130.00</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="20" customHeight="1">
       <x:c r="A21" s="2" t="str">
-        <x:v>X51006620161.png</x:v>
+        <x:v>receipt_0190.png</x:v>
       </x:c>
       <x:c r="B21" s="2" t="str">
-        <x:v>2016-02-28</x:v>
+        <x:v>2018-04-28</x:v>
       </x:c>
       <x:c r="C21" s="2" t="str">
-        <x:v>110.00</x:v>
+        <x:v>26.10</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
